--- a/data/trans_dic/P1804_2016_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1804_2016_2023-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,98</t>
+          <t>4,83; 10,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,97</t>
+          <t>0,43; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,65</t>
+          <t>10,45; 19,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,43</t>
+          <t>3,21; 6,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,02</t>
+          <t>8,28; 13,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,85</t>
+          <t>2,06; 4,34</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,8</t>
+          <t>2,95; 7,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,35</t>
+          <t>4,4; 8,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,65</t>
+          <t>0,93; 3,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,2</t>
+          <t>4,13; 7,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,16</t>
+          <t>0,58; 2,21</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,25</t>
+          <t>1,07; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,19</t>
+          <t>2,19; 5,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,84</t>
+          <t>2,34; 7,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,79</t>
+          <t>5,84; 10,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,07</t>
+          <t>2,21; 5,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,73</t>
+          <t>4,49; 7,62</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 25,82</t>
+          <t>17,39; 25,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 41,06</t>
+          <t>28,4; 41,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,82; 33,94</t>
+          <t>24,56; 34,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 34,12</t>
+          <t>29,76; 38,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,38; 29,05</t>
+          <t>22,07; 28,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 34,8</t>
+          <t>30,63; 38,12</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,29</t>
+          <t>1,38; 6,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,73</t>
+          <t>0,3; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,75</t>
+          <t>2,35; 8,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,21</t>
+          <t>0,8; 3,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,35</t>
+          <t>2,52; 6,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,52</t>
+          <t>0,7; 2,4</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1037,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,4</t>
+          <t>4,09; 9,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,26</t>
+          <t>1,24; 5,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,05</t>
+          <t>6,9; 12,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,94</t>
+          <t>0,52; 2,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,8</t>
+          <t>6,11; 9,74</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,79</t>
+          <t>3,23; 6,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,9</t>
+          <t>3,99; 8,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,34</t>
+          <t>5,19; 9,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 10,06</t>
+          <t>7,39; 11,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,42</t>
+          <t>4,66; 7,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,12</t>
+          <t>6,2; 9,01</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,7</t>
+          <t>4,29; 7,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,31</t>
+          <t>0,93; 2,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,26</t>
+          <t>7,76; 12,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,82</t>
+          <t>1,7; 3,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,34</t>
+          <t>6,57; 9,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,72</t>
+          <t>1,55; 3,04</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,26</t>
+          <t>5,44; 7,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,56</t>
+          <t>5,35; 7,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,05</t>
+          <t>8,83; 10,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,63</t>
+          <t>7,67; 9,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,86</t>
+          <t>7,43; 8,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,3</t>
+          <t>6,76; 8,05</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>18814</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14161; 32244</t>
+          <t>14196; 31013</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1626; 12351</t>
+          <t>1358; 9364</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29232; 53852</t>
+          <t>30179; 55671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6404; 15737</t>
+          <t>10134; 21868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49037; 81672</t>
+          <t>48240; 77213</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9953; 23136</t>
+          <t>13061; 27533</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>12504</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14387; 34185</t>
+          <t>14844; 35854</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 10070</t>
+          <t>0; 11547</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24308; 48885</t>
+          <t>23017; 45773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4613; 18757</t>
+          <t>5085; 19591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43164; 73808</t>
+          <t>42393; 73228</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5200; 22333</t>
+          <t>6231; 23819</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>39591</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3467; 13533</t>
+          <t>3393; 14296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6954; 19554</t>
+          <t>6924; 18671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8143; 23012</t>
+          <t>7859; 24533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19549; 37616</t>
+          <t>20777; 38435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14667; 33203</t>
+          <t>14489; 32816</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29229; 51350</t>
+          <t>30191; 51189</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>106275</t>
+          <t>128069</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124638</t>
+          <t>143629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>230912</t>
+          <t>271698</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63182; 95526</t>
+          <t>64351; 95564</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86804; 128327</t>
+          <t>105956; 155811</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96107; 131452</t>
+          <t>95111; 132582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80560; 162326</t>
+          <t>125574; 163350</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>169438; 219962</t>
+          <t>167107; 217368</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167287; 274305</t>
+          <t>243541; 303057</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5930</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2838; 13286</t>
+          <t>2912; 13221</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>599; 4878</t>
+          <t>623; 5560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5321; 19121</t>
+          <t>5136; 18988</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1821; 6703</t>
+          <t>1817; 7786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9810; 27282</t>
+          <t>10842; 27432</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2913; 9779</t>
+          <t>3039; 10385</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>41511</t>
         </is>
       </c>
     </row>
@@ -2101,27 +2101,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10787; 25349</t>
+          <t>11069; 24527</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2843; 14354</t>
+          <t>3377; 15082</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16283; 30968</t>
+          <t>18186; 34176</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2847; 15740</t>
+          <t>2801; 14326</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31423; 51618</t>
+          <t>32657; 52038</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>40484</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>70383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94460</t>
+          <t>110868</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22266; 44608</t>
+          <t>21208; 43550</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24350; 49334</t>
+          <t>28749; 58081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36318; 64558</t>
+          <t>35861; 64179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28424; 85164</t>
+          <t>56664; 85725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64123; 100025</t>
+          <t>62875; 99276</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60401; 119458</t>
+          <t>92091; 133916</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>35486</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33629; 59954</t>
+          <t>33397; 58301</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5077; 21452</t>
+          <t>7387; 23269</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62677; 101282</t>
+          <t>64122; 101847</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12840; 27425</t>
+          <t>14150; 30387</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>104212; 149828</t>
+          <t>105504; 151180</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18070; 44746</t>
+          <t>25305; 49526</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>276729</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>467563</t>
+          <t>536400</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>186939; 246481</t>
+          <t>184751; 243225</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>152011; 226927</t>
+          <t>189032; 258774</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>322187; 391829</t>
+          <t>312856; 388852</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>228617; 315698</t>
+          <t>286074; 351492</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>520169; 614524</t>
+          <t>515476; 615517</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>403907; 519745</t>
+          <t>491092; 584145</t>
         </is>
       </c>
     </row>
